--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_RMSEP.xlsx
@@ -1,211 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>RMSEP_glo</t>
-  </si>
-  <si>
-    <t>LV0_RMSEP</t>
-  </si>
-  <si>
-    <t>LV1_RMSEP</t>
-  </si>
-  <si>
-    <t>LV2_RMSEP</t>
-  </si>
-  <si>
-    <t>LV3_RMSEP</t>
-  </si>
-  <si>
-    <t>LV4_RMSEP</t>
-  </si>
-  <si>
-    <t>LV5_RMSEP</t>
-  </si>
-  <si>
-    <t>LV6_RMSEP</t>
-  </si>
-  <si>
-    <t>LV7_RMSEP</t>
-  </si>
-  <si>
-    <t>LV8_RMSEP</t>
-  </si>
-  <si>
-    <t>LV9_RMSEP</t>
-  </si>
-  <si>
-    <t>LV10_RMSEP</t>
-  </si>
-  <si>
-    <t>LV11_RMSEP</t>
-  </si>
-  <si>
-    <t>LV12_RMSEP</t>
-  </si>
-  <si>
-    <t>LV13_RMSEP</t>
-  </si>
-  <si>
-    <t>LV14_RMSEP</t>
-  </si>
-  <si>
-    <t>LV15_RMSEP</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -253,19 +63,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -307,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -339,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -374,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -550,2436 +350,2539 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RMSEP_glo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_RMSEP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_RMSEP</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_RMSEP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_RMSEP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_RMSEP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_RMSEP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_RMSEP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_RMSEP</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_RMSEP</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_RMSEP</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_RMSEP</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_RMSEP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_RMSEP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_RMSEP</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_RMSEP</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_RMSEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>0.10074533524608741</v>
+        <v>0.1007453405409815</v>
       </c>
       <c r="C2">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D2">
-        <v>0.11474316886067031</v>
+        <v>0.1147431749826151</v>
       </c>
       <c r="E2">
-        <v>0.1169266877764629</v>
+        <v>0.1169266958508553</v>
       </c>
       <c r="F2">
-        <v>0.11653063344658671</v>
+        <v>0.1165306413301746</v>
       </c>
       <c r="G2">
-        <v>0.11571086006006751</v>
+        <v>0.1157108672594978</v>
       </c>
       <c r="H2">
-        <v>0.11681831318556</v>
+        <v>0.1168183241776329</v>
       </c>
       <c r="I2">
-        <v>0.116678295857794</v>
+        <v>0.1166783026295964</v>
       </c>
       <c r="J2">
-        <v>0.11386998600773079</v>
+        <v>0.1138699919112775</v>
       </c>
       <c r="K2">
-        <v>0.11104446750009481</v>
+        <v>0.1110444730612827</v>
       </c>
       <c r="L2">
-        <v>0.112811662813421</v>
+        <v>0.1128116682054843</v>
       </c>
       <c r="M2">
-        <v>0.1098559070333642</v>
+        <v>0.1098559121902114</v>
       </c>
       <c r="N2">
-        <v>0.10496048144822941</v>
+        <v>0.1049604840658206</v>
       </c>
       <c r="O2">
-        <v>0.10339035028749891</v>
+        <v>0.1033903564934992</v>
       </c>
       <c r="P2">
-        <v>9.6294445458681141E-2</v>
+        <v>0.09629445169466083</v>
       </c>
       <c r="Q2">
-        <v>9.0801881004864124E-2</v>
+        <v>0.09080188596156544</v>
       </c>
       <c r="R2">
-        <v>8.7847525000461057E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
+        <v>0.08784752966596145</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>0.10453595679114069</v>
+        <v>0.1045359564943969</v>
       </c>
       <c r="C3">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D3">
-        <v>0.1131521446231661</v>
+        <v>0.113152150830424</v>
       </c>
       <c r="E3">
-        <v>0.12176567884221549</v>
+        <v>0.1217656883213459</v>
       </c>
       <c r="F3">
-        <v>0.1189970706614855</v>
+        <v>0.118997076516187</v>
       </c>
       <c r="G3">
-        <v>0.1106268300215289</v>
+        <v>0.1106268379721196</v>
       </c>
       <c r="H3">
-        <v>0.1061831940282489</v>
+        <v>0.1061832007523403</v>
       </c>
       <c r="I3">
-        <v>0.1032535602708884</v>
+        <v>0.103253559946325</v>
       </c>
       <c r="J3">
-        <v>9.9502270544923471E-2</v>
+        <v>0.09950227861535992</v>
       </c>
       <c r="K3">
-        <v>9.8142749979271332E-2</v>
+        <v>0.09814275394198771</v>
       </c>
       <c r="L3">
-        <v>9.5545468383762419E-2</v>
+        <v>0.09554547041761634</v>
       </c>
       <c r="M3">
-        <v>9.2757359618552804E-2</v>
+        <v>0.09275736011757302</v>
       </c>
       <c r="N3">
-        <v>9.3190697896147895E-2</v>
+        <v>0.09319069684607539</v>
       </c>
       <c r="O3">
-        <v>9.3232560747015816E-2</v>
+        <v>0.09323255623166947</v>
       </c>
       <c r="P3">
-        <v>9.4687519301892759E-2</v>
+        <v>0.09468750571592782</v>
       </c>
       <c r="Q3">
-        <v>9.5490615104019974E-2</v>
+        <v>0.09549059537240147</v>
       </c>
       <c r="R3">
-        <v>9.4422978006231437E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>20</v>
+        <v>0.09442295213069304</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>0.10855298964182319</v>
+        <v>0.1085529965265431</v>
       </c>
       <c r="C4">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D4">
-        <v>0.1144596864574192</v>
+        <v>0.1144596924264423</v>
       </c>
       <c r="E4">
-        <v>0.115795593779492</v>
+        <v>0.1157956063301064</v>
       </c>
       <c r="F4">
-        <v>0.1195880263654209</v>
+        <v>0.1195880326443584</v>
       </c>
       <c r="G4">
-        <v>0.11969560391143989</v>
+        <v>0.1196956105507237</v>
       </c>
       <c r="H4">
-        <v>0.12284540106926591</v>
+        <v>0.1228454057612969</v>
       </c>
       <c r="I4">
-        <v>0.116796774050342</v>
+        <v>0.1167967753015047</v>
       </c>
       <c r="J4">
-        <v>0.1119358299777853</v>
+        <v>0.1119358154605093</v>
       </c>
       <c r="K4">
-        <v>0.10927693259446759</v>
+        <v>0.109276941816799</v>
       </c>
       <c r="L4">
-        <v>0.1089855084401201</v>
+        <v>0.1089855092006146</v>
       </c>
       <c r="M4">
-        <v>0.10450716160972109</v>
+        <v>0.1045071514653649</v>
       </c>
       <c r="N4">
-        <v>9.9848589494845985E-2</v>
+        <v>0.09984859607272305</v>
       </c>
       <c r="O4">
-        <v>9.5885779738673307E-2</v>
+        <v>0.09588578283509193</v>
       </c>
       <c r="P4">
-        <v>9.3751950401671058E-2</v>
+        <v>0.09375195399450843</v>
       </c>
       <c r="Q4">
-        <v>9.3455228331505255E-2</v>
+        <v>0.0934552320524249</v>
       </c>
       <c r="R4">
-        <v>9.4896307688527248E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>21</v>
+        <v>0.09489631146771685</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>9.7062919336890721E-2</v>
+        <v>0.09706292222449264</v>
       </c>
       <c r="C5">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D5">
-        <v>0.113982307158368</v>
+        <v>0.1139823136467216</v>
       </c>
       <c r="E5">
-        <v>0.1176838667981034</v>
+        <v>0.1176838747493598</v>
       </c>
       <c r="F5">
-        <v>0.11511055679445691</v>
+        <v>0.1151105613125872</v>
       </c>
       <c r="G5">
-        <v>0.1201458174507531</v>
+        <v>0.1201458318677397</v>
       </c>
       <c r="H5">
-        <v>0.1087954348776006</v>
+        <v>0.1087954434051443</v>
       </c>
       <c r="I5">
-        <v>0.1038899344307832</v>
+        <v>0.1038899400992903</v>
       </c>
       <c r="J5">
-        <v>0.10094363936299409</v>
+        <v>0.1009436431442028</v>
       </c>
       <c r="K5">
-        <v>9.6192312165219659E-2</v>
+        <v>0.09619231674032157</v>
       </c>
       <c r="L5">
-        <v>9.1712762439917619E-2</v>
+        <v>0.09171276409799367</v>
       </c>
       <c r="M5">
-        <v>8.9736374597275223E-2</v>
+        <v>0.08973636981041096</v>
       </c>
       <c r="N5">
-        <v>8.7520346505902596E-2</v>
+        <v>0.08752034659904866</v>
       </c>
       <c r="O5">
-        <v>8.7364072120166211E-2</v>
+        <v>0.08736407036154867</v>
       </c>
       <c r="P5">
-        <v>8.9000358946309269E-2</v>
+        <v>0.08900035530253046</v>
       </c>
       <c r="Q5">
-        <v>9.0524254449830963E-2</v>
+        <v>0.09052424938756497</v>
       </c>
       <c r="R5">
-        <v>9.2122916023509527E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
+        <v>0.09212290847664896</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>9.535302884493238E-2</v>
+        <v>0.09535303973531363</v>
       </c>
       <c r="C6">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D6">
-        <v>0.11379468023501479</v>
+        <v>0.1137946865222441</v>
       </c>
       <c r="E6">
-        <v>0.11879714000245981</v>
+        <v>0.118797149536868</v>
       </c>
       <c r="F6">
-        <v>0.1164789704772153</v>
+        <v>0.1164789755745929</v>
       </c>
       <c r="G6">
-        <v>0.1181293403683754</v>
+        <v>0.1181293482786568</v>
       </c>
       <c r="H6">
-        <v>0.1058053693551733</v>
+        <v>0.1058053795696798</v>
       </c>
       <c r="I6">
-        <v>9.9635075533225079E-2</v>
+        <v>0.09963507951448504</v>
       </c>
       <c r="J6">
-        <v>9.6645586238692294E-2</v>
+        <v>0.09664559251586029</v>
       </c>
       <c r="K6">
-        <v>9.1179225932285418E-2</v>
+        <v>0.09117922809451856</v>
       </c>
       <c r="L6">
-        <v>8.8504844149698156E-2</v>
+        <v>0.08850484175025423</v>
       </c>
       <c r="M6">
-        <v>8.7457743649174552E-2</v>
+        <v>0.08745775428730382</v>
       </c>
       <c r="N6">
-        <v>8.5956222356893958E-2</v>
+        <v>0.08595622494927567</v>
       </c>
       <c r="O6">
-        <v>8.5544788218651621E-2</v>
+        <v>0.08554479032270416</v>
       </c>
       <c r="P6">
-        <v>8.6033545636729714E-2</v>
+        <v>0.08603354807790695</v>
       </c>
       <c r="Q6">
-        <v>8.5662654980660197E-2</v>
+        <v>0.08566265544018901</v>
       </c>
       <c r="R6">
-        <v>8.7319351168016313E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>23</v>
+        <v>0.08731935124221506</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>0.1056711089791834</v>
+        <v>0.1056711183690292</v>
       </c>
       <c r="C7">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D7">
-        <v>0.1146016142590533</v>
+        <v>0.1146016202852867</v>
       </c>
       <c r="E7">
-        <v>0.1161403595458933</v>
+        <v>0.1161403659585213</v>
       </c>
       <c r="F7">
-        <v>0.1199547054787436</v>
+        <v>0.1199547102629344</v>
       </c>
       <c r="G7">
-        <v>0.1211274474980554</v>
+        <v>0.1211274554463296</v>
       </c>
       <c r="H7">
-        <v>0.12443081762492721</v>
+        <v>0.1244308239840566</v>
       </c>
       <c r="I7">
-        <v>0.1219474260250016</v>
+        <v>0.1219474229912373</v>
       </c>
       <c r="J7">
-        <v>0.1160838357405268</v>
+        <v>0.1160838403767665</v>
       </c>
       <c r="K7">
-        <v>0.11058198576776029</v>
+        <v>0.1105819897139188</v>
       </c>
       <c r="L7">
-        <v>0.10965356109780949</v>
+        <v>0.1096535668120827</v>
       </c>
       <c r="M7">
-        <v>0.1081527745926955</v>
+        <v>0.1081527826272147</v>
       </c>
       <c r="N7">
-        <v>0.1017220960585954</v>
+        <v>0.1017221018906103</v>
       </c>
       <c r="O7">
-        <v>9.6899409251567023E-2</v>
+        <v>0.09689941232470674</v>
       </c>
       <c r="P7">
-        <v>9.3378368127338823E-2</v>
+        <v>0.0933783719854256</v>
       </c>
       <c r="Q7">
-        <v>9.1566403006230465E-2</v>
+        <v>0.09156640706724256</v>
       </c>
       <c r="R7">
-        <v>9.1325267683452671E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>24</v>
+        <v>0.09132527165025003</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>0.1017445451562395</v>
+        <v>0.1017445478332352</v>
       </c>
       <c r="C8">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D8">
-        <v>0.11431264567133009</v>
+        <v>0.1143126515204076</v>
       </c>
       <c r="E8">
-        <v>0.1159916195215073</v>
+        <v>0.1159916262190161</v>
       </c>
       <c r="F8">
-        <v>0.1193977979402966</v>
+        <v>0.1193978094967765</v>
       </c>
       <c r="G8">
-        <v>0.1213040832062017</v>
+        <v>0.1213040869548936</v>
       </c>
       <c r="H8">
-        <v>0.1187690207101593</v>
+        <v>0.1187690267248046</v>
       </c>
       <c r="I8">
-        <v>0.11274389984410441</v>
+        <v>0.1127439028491473</v>
       </c>
       <c r="J8">
-        <v>0.1121470639365372</v>
+        <v>0.1121470694586522</v>
       </c>
       <c r="K8">
-        <v>0.106105252114838</v>
+        <v>0.1061052545186625</v>
       </c>
       <c r="L8">
-        <v>0.1035601531079402</v>
+        <v>0.1035601541546041</v>
       </c>
       <c r="M8">
-        <v>9.5885409162292198E-2</v>
+        <v>0.09588541080544348</v>
       </c>
       <c r="N8">
-        <v>9.5221230650269773E-2</v>
+        <v>0.0952212328965043</v>
       </c>
       <c r="O8">
-        <v>9.2037939106321867E-2</v>
+        <v>0.0920379426183387</v>
       </c>
       <c r="P8">
-        <v>9.0740251425464685E-2</v>
+        <v>0.090740255275101</v>
       </c>
       <c r="Q8">
-        <v>9.0628848518383348E-2</v>
+        <v>0.09062885294113673</v>
       </c>
       <c r="R8">
-        <v>9.1626508016745559E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>25</v>
+        <v>0.09162651190827034</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>9.8111444324546895E-2</v>
+        <v>0.09811144799058952</v>
       </c>
       <c r="C9">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D9">
-        <v>0.1141846288863476</v>
+        <v>0.1141846348233442</v>
       </c>
       <c r="E9">
-        <v>0.11572695657856109</v>
+        <v>0.1157269654261977</v>
       </c>
       <c r="F9">
-        <v>0.1196543104283479</v>
+        <v>0.1196543165995057</v>
       </c>
       <c r="G9">
-        <v>0.12123744638550051</v>
+        <v>0.121237448437486</v>
       </c>
       <c r="H9">
-        <v>0.11833507680793171</v>
+        <v>0.1183350827603839</v>
       </c>
       <c r="I9">
-        <v>0.11251517533704709</v>
+        <v>0.1125151889255851</v>
       </c>
       <c r="J9">
-        <v>0.1122243672333101</v>
+        <v>0.1122243700286066</v>
       </c>
       <c r="K9">
-        <v>0.1061198546991186</v>
+        <v>0.10611986021683</v>
       </c>
       <c r="L9">
-        <v>0.1044810552169243</v>
+        <v>0.1044810563494607</v>
       </c>
       <c r="M9">
-        <v>9.4660512395434895E-2</v>
+        <v>0.09466051594493032</v>
       </c>
       <c r="N9">
-        <v>9.5273279634058947E-2</v>
+        <v>0.09527328415758955</v>
       </c>
       <c r="O9">
-        <v>9.2576185752868467E-2</v>
+        <v>0.0925761900354322</v>
       </c>
       <c r="P9">
-        <v>9.0588613012175995E-2</v>
+        <v>0.09058861858419165</v>
       </c>
       <c r="Q9">
-        <v>9.0448652851135361E-2</v>
+        <v>0.09044865853785861</v>
       </c>
       <c r="R9">
-        <v>9.052833057521173E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>26</v>
+        <v>0.090528336120835</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>9.9166043095581247E-2</v>
+        <v>0.09916604739099666</v>
       </c>
       <c r="C10">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D10">
-        <v>0.1140906845901169</v>
+        <v>0.1140906906081123</v>
       </c>
       <c r="E10">
-        <v>0.11548756087933409</v>
+        <v>0.115487568220872</v>
       </c>
       <c r="F10">
-        <v>0.1189450582230865</v>
+        <v>0.1189450712810521</v>
       </c>
       <c r="G10">
-        <v>0.1200335987645501</v>
+        <v>0.1200336002810437</v>
       </c>
       <c r="H10">
-        <v>0.1175056513171287</v>
+        <v>0.1175056566583849</v>
       </c>
       <c r="I10">
-        <v>0.111784532743144</v>
+        <v>0.1117845371413638</v>
       </c>
       <c r="J10">
-        <v>0.11101870529922619</v>
+        <v>0.1110187106934434</v>
       </c>
       <c r="K10">
-        <v>0.1054851247691671</v>
+        <v>0.1054851269877143</v>
       </c>
       <c r="L10">
-        <v>0.10388237120389129</v>
+        <v>0.1038823724927125</v>
       </c>
       <c r="M10">
-        <v>9.4565476934924425E-2</v>
+        <v>0.09456548137972555</v>
       </c>
       <c r="N10">
-        <v>9.4959865313171909E-2</v>
+        <v>0.09495987016766984</v>
       </c>
       <c r="O10">
-        <v>9.1993970425816363E-2</v>
+        <v>0.0919939739246196</v>
       </c>
       <c r="P10">
-        <v>9.0312700342573243E-2</v>
+        <v>0.09031270562598953</v>
       </c>
       <c r="Q10">
-        <v>9.069874215139756E-2</v>
+        <v>0.09069874712359909</v>
       </c>
       <c r="R10">
-        <v>9.1038394461527505E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>27</v>
+        <v>0.09103839940248351</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>9.9736137439300307E-2</v>
+        <v>0.09973614205901135</v>
       </c>
       <c r="C11">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D11">
-        <v>0.11435662979712009</v>
+        <v>0.114356635747978</v>
       </c>
       <c r="E11">
-        <v>0.11581351251776011</v>
+        <v>0.1158135205402333</v>
       </c>
       <c r="F11">
-        <v>0.1193881103059159</v>
+        <v>0.1193881284719051</v>
       </c>
       <c r="G11">
-        <v>0.1211106492782958</v>
+        <v>0.1211106532200258</v>
       </c>
       <c r="H11">
-        <v>0.11840499682282921</v>
+        <v>0.1184050032981179</v>
       </c>
       <c r="I11">
-        <v>0.1131494861317241</v>
+        <v>0.1131494902366074</v>
       </c>
       <c r="J11">
-        <v>0.1127498755102407</v>
+        <v>0.1127499127797541</v>
       </c>
       <c r="K11">
-        <v>0.10720847536031081</v>
+        <v>0.1072077957445974</v>
       </c>
       <c r="L11">
-        <v>0.1052908372314454</v>
+        <v>0.1052907398804798</v>
       </c>
       <c r="M11">
-        <v>9.5171325599797088E-2</v>
+        <v>0.09517133023933935</v>
       </c>
       <c r="N11">
-        <v>9.4962282316320965E-2</v>
+        <v>0.09496228716463709</v>
       </c>
       <c r="O11">
-        <v>9.2091196837436037E-2</v>
+        <v>0.09209120132232132</v>
       </c>
       <c r="P11">
-        <v>9.042965606573436E-2</v>
+        <v>0.09042966133534075</v>
       </c>
       <c r="Q11">
-        <v>9.0533599997859371E-2</v>
+        <v>0.09053360528136857</v>
       </c>
       <c r="R11">
-        <v>9.0358184869832422E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>28</v>
+        <v>0.09035818982309331</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>9.3894809711328769E-2</v>
+        <v>0.09389481519417148</v>
       </c>
       <c r="C12">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D12">
-        <v>0.1137530238588897</v>
+        <v>0.1137530300154388</v>
       </c>
       <c r="E12">
-        <v>0.1169970902391765</v>
+        <v>0.1169970979497156</v>
       </c>
       <c r="F12">
-        <v>0.11478062600258471</v>
+        <v>0.1147806316366113</v>
       </c>
       <c r="G12">
-        <v>0.1194825833697912</v>
+        <v>0.1194825909947408</v>
       </c>
       <c r="H12">
-        <v>0.1102109921657588</v>
+        <v>0.1102109992566545</v>
       </c>
       <c r="I12">
-        <v>0.1065470345773827</v>
+        <v>0.1065470413795047</v>
       </c>
       <c r="J12">
-        <v>0.1002997695152089</v>
+        <v>0.1002997740729894</v>
       </c>
       <c r="K12">
-        <v>9.3775762278168834E-2</v>
+        <v>0.09377576781795414</v>
       </c>
       <c r="L12">
-        <v>8.9569714511131937E-2</v>
+        <v>0.08956971615062018</v>
       </c>
       <c r="M12">
-        <v>8.7530192349057567E-2</v>
+        <v>0.08753019127319359</v>
       </c>
       <c r="N12">
-        <v>8.5284584402482669E-2</v>
+        <v>0.08528458150658744</v>
       </c>
       <c r="O12">
-        <v>8.4875677386903894E-2</v>
+        <v>0.08487567459766777</v>
       </c>
       <c r="P12">
-        <v>8.633783171472148E-2</v>
+        <v>0.08633782809345565</v>
       </c>
       <c r="Q12">
-        <v>8.7599277363285932E-2</v>
+        <v>0.08759927156860961</v>
       </c>
       <c r="R12">
-        <v>9.0137947022308471E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>29</v>
+        <v>0.09013793859193971</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>0.111910177232286</v>
+        <v>0.111910183934505</v>
       </c>
       <c r="C13">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D13">
-        <v>0.1143886023057599</v>
+        <v>0.1143886090360323</v>
       </c>
       <c r="E13">
-        <v>0.12166474741867379</v>
+        <v>0.1216647555707302</v>
       </c>
       <c r="F13">
-        <v>0.11807267514169489</v>
+        <v>0.1180726807616046</v>
       </c>
       <c r="G13">
-        <v>0.12060304967898069</v>
+        <v>0.1206030610786805</v>
       </c>
       <c r="H13">
-        <v>0.1204709329421972</v>
+        <v>0.1204709415928463</v>
       </c>
       <c r="I13">
-        <v>0.1126214349096059</v>
+        <v>0.1126214422208431</v>
       </c>
       <c r="J13">
-        <v>0.1120623446298214</v>
+        <v>0.1120623531660903</v>
       </c>
       <c r="K13">
-        <v>0.1091852895432468</v>
+        <v>0.1091852975811869</v>
       </c>
       <c r="L13">
-        <v>0.10440339634572809</v>
+        <v>0.1044034032163702</v>
       </c>
       <c r="M13">
-        <v>9.9775174033168615E-2</v>
+        <v>0.09977517743590973</v>
       </c>
       <c r="N13">
-        <v>9.8932248350893398E-2</v>
+        <v>0.09893225081262544</v>
       </c>
       <c r="O13">
-        <v>9.7298969158670867E-2</v>
+        <v>0.09729897009188873</v>
       </c>
       <c r="P13">
-        <v>9.7188554022300838E-2</v>
+        <v>0.0971885527371576</v>
       </c>
       <c r="Q13">
-        <v>9.5715165456428303E-2</v>
+        <v>0.09571516009064665</v>
       </c>
       <c r="R13">
-        <v>9.6357158171281709E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>30</v>
+        <v>0.09635715110811635</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>9.6987064940827344E-2</v>
+        <v>0.09698707016606434</v>
       </c>
       <c r="C14">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D14">
-        <v>0.1144267078343895</v>
+        <v>0.1144267136758955</v>
       </c>
       <c r="E14">
-        <v>0.1158149683698908</v>
+        <v>0.1158149757069763</v>
       </c>
       <c r="F14">
-        <v>0.1194893574616282</v>
+        <v>0.1194893638653122</v>
       </c>
       <c r="G14">
-        <v>0.1207482062014273</v>
+        <v>0.1207482171319852</v>
       </c>
       <c r="H14">
-        <v>0.1236745406399149</v>
+        <v>0.1236745514585559</v>
       </c>
       <c r="I14">
-        <v>0.1211824859043137</v>
+        <v>0.1211824894431234</v>
       </c>
       <c r="J14">
-        <v>0.115651071806877</v>
+        <v>0.1156510781256544</v>
       </c>
       <c r="K14">
-        <v>0.1107187579479378</v>
+        <v>0.1107187636608434</v>
       </c>
       <c r="L14">
-        <v>0.1090014999385253</v>
+        <v>0.1090015062531322</v>
       </c>
       <c r="M14">
-        <v>0.1078035761921399</v>
+        <v>0.1078035750059145</v>
       </c>
       <c r="N14">
-        <v>0.1012796082184531</v>
+        <v>0.1012796220900107</v>
       </c>
       <c r="O14">
-        <v>9.4345743105839278E-2</v>
+        <v>0.09434574822731621</v>
       </c>
       <c r="P14">
-        <v>9.1589997006349996E-2</v>
+        <v>0.09159000173651823</v>
       </c>
       <c r="Q14">
-        <v>8.9676759181677432E-2</v>
+        <v>0.08967676359558129</v>
       </c>
       <c r="R14">
-        <v>8.8068545814845772E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>31</v>
+        <v>0.08806855081357703</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>0.1030630285453431</v>
+        <v>0.1030630340968266</v>
       </c>
       <c r="C15">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D15">
-        <v>0.1142452868669334</v>
+        <v>0.1142452927950884</v>
       </c>
       <c r="E15">
-        <v>0.1155508234969304</v>
+        <v>0.1155508308079916</v>
       </c>
       <c r="F15">
-        <v>0.11891134785117111</v>
+        <v>0.1189113579500137</v>
       </c>
       <c r="G15">
-        <v>0.11968849616309291</v>
+        <v>0.1196885032103601</v>
       </c>
       <c r="H15">
-        <v>0.1222493882881116</v>
+        <v>0.1222493933769391</v>
       </c>
       <c r="I15">
-        <v>0.12006087624405939</v>
+        <v>0.1200608744584132</v>
       </c>
       <c r="J15">
-        <v>0.11436432906227149</v>
+        <v>0.1143643317181599</v>
       </c>
       <c r="K15">
-        <v>0.1105881207498572</v>
+        <v>0.1105881259903493</v>
       </c>
       <c r="L15">
-        <v>0.1088275624772633</v>
+        <v>0.108827568319778</v>
       </c>
       <c r="M15">
-        <v>0.1080989505856077</v>
+        <v>0.1080989567523251</v>
       </c>
       <c r="N15">
-        <v>0.102529495640886</v>
+        <v>0.1025295004546978</v>
       </c>
       <c r="O15">
-        <v>9.5936941021150565E-2</v>
+        <v>0.09593694641123923</v>
       </c>
       <c r="P15">
-        <v>9.3373153131830255E-2</v>
+        <v>0.09337315833372797</v>
       </c>
       <c r="Q15">
-        <v>9.1772147613578062E-2</v>
+        <v>0.09177215286800534</v>
       </c>
       <c r="R15">
-        <v>9.0444588357373262E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>32</v>
+        <v>0.09044459386726141</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>0.10256858283602741</v>
+        <v>0.1025685880105099</v>
       </c>
       <c r="C16">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D16">
-        <v>0.1146285380434138</v>
+        <v>0.1146285439248382</v>
       </c>
       <c r="E16">
-        <v>0.1160705047518468</v>
+        <v>0.1160705106444966</v>
       </c>
       <c r="F16">
-        <v>0.11949074223956289</v>
+        <v>0.1194907477073706</v>
       </c>
       <c r="G16">
-        <v>0.12037129298694051</v>
+        <v>0.1203712996710645</v>
       </c>
       <c r="H16">
-        <v>0.1231874685207746</v>
+        <v>0.123187472503348</v>
       </c>
       <c r="I16">
-        <v>0.120834916541752</v>
+        <v>0.1208349188433465</v>
       </c>
       <c r="J16">
-        <v>0.1151493736674036</v>
+        <v>0.1151493784259519</v>
       </c>
       <c r="K16">
-        <v>0.11047961474903691</v>
+        <v>0.1104796211295315</v>
       </c>
       <c r="L16">
-        <v>0.1093115480413472</v>
+        <v>0.1093115528114876</v>
       </c>
       <c r="M16">
-        <v>0.1083910683874489</v>
+        <v>0.1083910776731009</v>
       </c>
       <c r="N16">
-        <v>0.1029550883441725</v>
+        <v>0.1029550887410354</v>
       </c>
       <c r="O16">
-        <v>9.6176197275307546E-2</v>
+        <v>0.09617620058456793</v>
       </c>
       <c r="P16">
-        <v>9.3301055971280814E-2</v>
+        <v>0.09330106094144475</v>
       </c>
       <c r="Q16">
-        <v>9.108487454358212E-2</v>
+        <v>0.09108487921734354</v>
       </c>
       <c r="R16">
-        <v>8.9599496599063799E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>33</v>
+        <v>0.08959950258098245</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>0.1044141248895238</v>
+        <v>0.1044140320675653</v>
       </c>
       <c r="C17">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D17">
-        <v>0.11436758860403549</v>
+        <v>0.1143675945692629</v>
       </c>
       <c r="E17">
-        <v>0.1153782311601905</v>
+        <v>0.1153782385432861</v>
       </c>
       <c r="F17">
-        <v>0.1188549850810199</v>
+        <v>0.1188549909945413</v>
       </c>
       <c r="G17">
-        <v>0.1196956215938378</v>
+        <v>0.119695626998247</v>
       </c>
       <c r="H17">
-        <v>0.1228721011455729</v>
+        <v>0.1228721086258047</v>
       </c>
       <c r="I17">
-        <v>0.12067822786357869</v>
+        <v>0.1206782452336697</v>
       </c>
       <c r="J17">
-        <v>0.1155374084033764</v>
+        <v>0.1155374149794569</v>
       </c>
       <c r="K17">
-        <v>0.1115075193515588</v>
+        <v>0.1115075254993208</v>
       </c>
       <c r="L17">
-        <v>0.10953042513970949</v>
+        <v>0.1095304305216093</v>
       </c>
       <c r="M17">
-        <v>0.1091455307285407</v>
+        <v>0.1091455330164125</v>
       </c>
       <c r="N17">
-        <v>0.10383884219683</v>
+        <v>0.1038387582988404</v>
       </c>
       <c r="O17">
-        <v>9.7721950773789007E-2</v>
+        <v>0.09772186375880886</v>
       </c>
       <c r="P17">
-        <v>9.5115325845606488E-2</v>
+        <v>0.0951153324877419</v>
       </c>
       <c r="Q17">
-        <v>9.3165731628396489E-2</v>
+        <v>0.09316573574650888</v>
       </c>
       <c r="R17">
-        <v>9.1069976488499779E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>34</v>
+        <v>0.09106998148183064</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>9.3800781360275351E-2</v>
+        <v>0.09380078334618855</v>
       </c>
       <c r="C18">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D18">
-        <v>0.1138702089437949</v>
+        <v>0.1138702151443388</v>
       </c>
       <c r="E18">
-        <v>0.11763925155594369</v>
+        <v>0.1176392575124602</v>
       </c>
       <c r="F18">
-        <v>0.11471028799371839</v>
+        <v>0.114710290293945</v>
       </c>
       <c r="G18">
-        <v>0.12012510016734559</v>
+        <v>0.120125108552371</v>
       </c>
       <c r="H18">
-        <v>0.108598082510734</v>
+        <v>0.1085980913048011</v>
       </c>
       <c r="I18">
-        <v>0.1044842888734487</v>
+        <v>0.1044842954538762</v>
       </c>
       <c r="J18">
-        <v>9.9757442208756569E-2</v>
+        <v>0.0997574464633684</v>
       </c>
       <c r="K18">
-        <v>9.3761975028775424E-2</v>
+        <v>0.0937619786700077</v>
       </c>
       <c r="L18">
-        <v>8.9030145573452735E-2</v>
+        <v>0.08903014765467344</v>
       </c>
       <c r="M18">
-        <v>8.7904704598455868E-2</v>
+        <v>0.08790470518337731</v>
       </c>
       <c r="N18">
-        <v>8.6019993350362922E-2</v>
+        <v>0.08601999435338863</v>
       </c>
       <c r="O18">
-        <v>8.5669646611440886E-2</v>
+        <v>0.085669644110889</v>
       </c>
       <c r="P18">
-        <v>8.7691339055780332E-2</v>
+        <v>0.08769133542212615</v>
       </c>
       <c r="Q18">
-        <v>8.9108681819719204E-2</v>
+        <v>0.08910867656116112</v>
       </c>
       <c r="R18">
-        <v>9.0667365636248567E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>35</v>
+        <v>0.09066735783406644</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>9.3323429579700273E-2</v>
+        <v>0.09332343378100053</v>
       </c>
       <c r="C19">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D19">
-        <v>0.1144819166563105</v>
+        <v>0.1144819238052178</v>
       </c>
       <c r="E19">
-        <v>0.11953116201897721</v>
+        <v>0.1195311706680489</v>
       </c>
       <c r="F19">
-        <v>0.1173216725618297</v>
+        <v>0.1173216782940571</v>
       </c>
       <c r="G19">
-        <v>0.1191971206640552</v>
+        <v>0.1191971318158423</v>
       </c>
       <c r="H19">
-        <v>0.1052505316439422</v>
+        <v>0.1052505380699182</v>
       </c>
       <c r="I19">
-        <v>9.9881759776950768E-2</v>
+        <v>0.09988176703616485</v>
       </c>
       <c r="J19">
-        <v>9.6182023030538008E-2</v>
+        <v>0.09618202897262082</v>
       </c>
       <c r="K19">
-        <v>9.0520517150302182E-2</v>
+        <v>0.09052052111663482</v>
       </c>
       <c r="L19">
-        <v>8.6964040643799645E-2</v>
+        <v>0.08696404360206844</v>
       </c>
       <c r="M19">
-        <v>8.6038447424794842E-2</v>
+        <v>0.08603845071406284</v>
       </c>
       <c r="N19">
-        <v>8.4042286236798519E-2</v>
+        <v>0.08404228952067541</v>
       </c>
       <c r="O19">
-        <v>8.4259970058911116E-2</v>
+        <v>0.08425997340482377</v>
       </c>
       <c r="P19">
-        <v>8.5124987991877954E-2</v>
+        <v>0.08512499135738273</v>
       </c>
       <c r="Q19">
-        <v>8.4607798025736605E-2</v>
+        <v>0.08460780029303394</v>
       </c>
       <c r="R19">
-        <v>8.5224297077116568E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>36</v>
+        <v>0.08522429730615974</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>9.3626207817703755E-2</v>
+        <v>0.09362621018244469</v>
       </c>
       <c r="C20">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D20">
-        <v>0.1140752258591267</v>
+        <v>0.1140752317968447</v>
       </c>
       <c r="E20">
-        <v>0.11994826136594371</v>
+        <v>0.1199482711486405</v>
       </c>
       <c r="F20">
-        <v>0.11782802566679861</v>
+        <v>0.1178280319349926</v>
       </c>
       <c r="G20">
-        <v>0.11295321590523121</v>
+        <v>0.1129532167346557</v>
       </c>
       <c r="H20">
-        <v>0.10604723911407909</v>
+        <v>0.1060472431147805</v>
       </c>
       <c r="I20">
-        <v>0.1038571668924268</v>
+        <v>0.1038571721952275</v>
       </c>
       <c r="J20">
-        <v>9.7741100025395627E-2</v>
+        <v>0.09774110365304062</v>
       </c>
       <c r="K20">
-        <v>9.2812668028109002E-2</v>
+        <v>0.09281267018260002</v>
       </c>
       <c r="L20">
-        <v>9.0320015244098217E-2</v>
+        <v>0.09032001806126694</v>
       </c>
       <c r="M20">
-        <v>8.6861345062426085E-2</v>
+        <v>0.08686134733876909</v>
       </c>
       <c r="N20">
-        <v>8.6638097199897068E-2</v>
+        <v>0.08663810141043082</v>
       </c>
       <c r="O20">
-        <v>8.6239295765171531E-2</v>
+        <v>0.08623929963678456</v>
       </c>
       <c r="P20">
-        <v>8.3552638629354498E-2</v>
+        <v>0.08355264144852816</v>
       </c>
       <c r="Q20">
-        <v>8.3385266925074392E-2</v>
+        <v>0.0833852678863389</v>
       </c>
       <c r="R20">
-        <v>8.3180640462912125E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>37</v>
+        <v>0.0831806411144302</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>0.1073244677315648</v>
+        <v>0.1073244710097576</v>
       </c>
       <c r="C21">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D21">
-        <v>0.1132726668675908</v>
+        <v>0.113272673051266</v>
       </c>
       <c r="E21">
-        <v>0.1222616949496951</v>
+        <v>0.1222617045483989</v>
       </c>
       <c r="F21">
-        <v>0.1193424310921215</v>
+        <v>0.1193424363639703</v>
       </c>
       <c r="G21">
-        <v>0.11255523351835971</v>
+        <v>0.1125552430711247</v>
       </c>
       <c r="H21">
-        <v>0.1085528220598722</v>
+        <v>0.1085528126113075</v>
       </c>
       <c r="I21">
-        <v>0.1067082348382434</v>
+        <v>0.1067082387038641</v>
       </c>
       <c r="J21">
-        <v>0.1036623220746072</v>
+        <v>0.1036623329821165</v>
       </c>
       <c r="K21">
-        <v>0.10041646268018201</v>
+        <v>0.1004164657379707</v>
       </c>
       <c r="L21">
-        <v>9.5967896384794277E-2</v>
+        <v>0.09596789611879696</v>
       </c>
       <c r="M21">
-        <v>9.3572588480293886E-2</v>
+        <v>0.09357258656199217</v>
       </c>
       <c r="N21">
-        <v>9.2664886527141332E-2</v>
+        <v>0.09266488141218127</v>
       </c>
       <c r="O21">
-        <v>9.3622480953009748E-2</v>
+        <v>0.0936224714723335</v>
       </c>
       <c r="P21">
-        <v>9.6167886280456652E-2</v>
+        <v>0.09616787134739463</v>
       </c>
       <c r="Q21">
-        <v>9.7637415047089338E-2</v>
+        <v>0.09763739283998345</v>
       </c>
       <c r="R21">
-        <v>9.686269992161671E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>38</v>
+        <v>0.09686267328525466</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>0.1110671199427436</v>
+        <v>0.1110671232969087</v>
       </c>
       <c r="C22">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D22">
-        <v>0.1133080264510096</v>
+        <v>0.1133080326530644</v>
       </c>
       <c r="E22">
-        <v>0.1217944924482075</v>
+        <v>0.1217945023434907</v>
       </c>
       <c r="F22">
-        <v>0.1189069685396308</v>
+        <v>0.1189069752033641</v>
       </c>
       <c r="G22">
-        <v>0.1120039083024003</v>
+        <v>0.1120039146221099</v>
       </c>
       <c r="H22">
-        <v>0.1090111621986905</v>
+        <v>0.1090111680077371</v>
       </c>
       <c r="I22">
-        <v>0.10751493477482529</v>
+        <v>0.1075149450606649</v>
       </c>
       <c r="J22">
-        <v>0.1060682651940424</v>
+        <v>0.1060682684383871</v>
       </c>
       <c r="K22">
-        <v>0.10485642279323169</v>
+        <v>0.1048564240040286</v>
       </c>
       <c r="L22">
-        <v>0.1003584090932378</v>
+        <v>0.1003584069379851</v>
       </c>
       <c r="M22">
-        <v>9.7670445299383762E-2</v>
+        <v>0.09767044165420291</v>
       </c>
       <c r="N22">
-        <v>9.6154246124238965E-2</v>
+        <v>0.09615423991978703</v>
       </c>
       <c r="O22">
-        <v>9.5429719543215011E-2</v>
+        <v>0.09542970807304198</v>
       </c>
       <c r="P22">
-        <v>9.6589650571664881E-2</v>
+        <v>0.09658963150572941</v>
       </c>
       <c r="Q22">
-        <v>9.7030291485610015E-2</v>
+        <v>0.09703026634311532</v>
       </c>
       <c r="R22">
-        <v>9.7351786144229666E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>39</v>
+        <v>0.09735175564273997</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>9.7211614046188943E-2</v>
+        <v>0.09721161838607796</v>
       </c>
       <c r="C23">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D23">
-        <v>0.1138221115894377</v>
+        <v>0.1138221191250794</v>
       </c>
       <c r="E23">
-        <v>0.1201859622228298</v>
+        <v>0.1201859662608228</v>
       </c>
       <c r="F23">
-        <v>0.1139078990618235</v>
+        <v>0.1139079074879185</v>
       </c>
       <c r="G23">
-        <v>0.1077169529721041</v>
+        <v>0.1077169535105766</v>
       </c>
       <c r="H23">
-        <v>9.9595279311786314E-2</v>
+        <v>0.09959527343935293</v>
       </c>
       <c r="I23">
-        <v>9.4002170185956482E-2</v>
+        <v>0.09400217449603911</v>
       </c>
       <c r="J23">
-        <v>9.1923021968757512E-2</v>
+        <v>0.09192302503427144</v>
       </c>
       <c r="K23">
-        <v>9.0997556123549442E-2</v>
+        <v>0.09099755667046418</v>
       </c>
       <c r="L23">
-        <v>8.9362936612053315E-2</v>
+        <v>0.08936293324045202</v>
       </c>
       <c r="M23">
-        <v>8.892964299746331E-2</v>
+        <v>0.08892963116516632</v>
       </c>
       <c r="N23">
-        <v>8.8921455840010835E-2</v>
+        <v>0.08892143840712939</v>
       </c>
       <c r="O23">
-        <v>8.9721296868493797E-2</v>
+        <v>0.08972127233961025</v>
       </c>
       <c r="P23">
-        <v>9.0303617393644606E-2</v>
+        <v>0.09030358916164304</v>
       </c>
       <c r="Q23">
-        <v>9.013297193655756E-2</v>
+        <v>0.09013294345673413</v>
       </c>
       <c r="R23">
-        <v>9.1667695517245421E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>40</v>
+        <v>0.09166766758057096</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>0.1119664178590343</v>
+        <v>0.1119664208170627</v>
       </c>
       <c r="C24">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D24">
-        <v>0.1158906923053451</v>
+        <v>0.1158906983293325</v>
       </c>
       <c r="E24">
-        <v>0.1191369586194152</v>
+        <v>0.1191369622614706</v>
       </c>
       <c r="F24">
-        <v>0.122232122272036</v>
+        <v>0.1222321293995771</v>
       </c>
       <c r="G24">
-        <v>0.11999862843207119</v>
+        <v>0.1199986315702511</v>
       </c>
       <c r="H24">
-        <v>0.1190436530041203</v>
+        <v>0.1190436576335054</v>
       </c>
       <c r="I24">
-        <v>0.1161321866190962</v>
+        <v>0.1161321894378211</v>
       </c>
       <c r="J24">
-        <v>0.1183916088294952</v>
+        <v>0.1183916147630239</v>
       </c>
       <c r="K24">
-        <v>0.11562181786430351</v>
+        <v>0.1156218372072784</v>
       </c>
       <c r="L24">
-        <v>0.106562061394637</v>
+        <v>0.1065620680696353</v>
       </c>
       <c r="M24">
-        <v>0.1007084790493246</v>
+        <v>0.1007084794941314</v>
       </c>
       <c r="N24">
-        <v>9.8878217647735009E-2</v>
+        <v>0.09887821376036683</v>
       </c>
       <c r="O24">
-        <v>0.10018368569140609</v>
+        <v>0.1001836740006047</v>
       </c>
       <c r="P24">
-        <v>0.10407607897484041</v>
+        <v>0.1040760615309355</v>
       </c>
       <c r="Q24">
-        <v>0.1076741266939294</v>
+        <v>0.1076741053627277</v>
       </c>
       <c r="R24">
-        <v>0.11243122878855</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>41</v>
+        <v>0.1124312017194077</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>0.1132015679960662</v>
+        <v>0.1132015713445403</v>
       </c>
       <c r="C25">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D25">
-        <v>0.1157551716374307</v>
+        <v>0.1157551780558525</v>
       </c>
       <c r="E25">
-        <v>0.11885820162959811</v>
+        <v>0.118858202575161</v>
       </c>
       <c r="F25">
-        <v>0.1219971011164744</v>
+        <v>0.1219971089795181</v>
       </c>
       <c r="G25">
-        <v>0.1194605859876218</v>
+        <v>0.1194605929429852</v>
       </c>
       <c r="H25">
-        <v>0.1183169958352572</v>
+        <v>0.1183169991294935</v>
       </c>
       <c r="I25">
-        <v>0.1173948609064845</v>
+        <v>0.1173948670965808</v>
       </c>
       <c r="J25">
-        <v>0.1226787684368148</v>
+        <v>0.1226787738775994</v>
       </c>
       <c r="K25">
-        <v>0.11971061833233849</v>
+        <v>0.1197106245159612</v>
       </c>
       <c r="L25">
-        <v>0.11496528251527489</v>
+        <v>0.1149652864380773</v>
       </c>
       <c r="M25">
-        <v>0.1030211150046501</v>
+        <v>0.1030211155096762</v>
       </c>
       <c r="N25">
-        <v>0.1010643309472274</v>
+        <v>0.1010643301718233</v>
       </c>
       <c r="O25">
-        <v>0.10013480516784699</v>
+        <v>0.1001347989451367</v>
       </c>
       <c r="P25">
-        <v>0.1026576258311048</v>
+        <v>0.102657614366834</v>
       </c>
       <c r="Q25">
-        <v>0.1057936171719925</v>
+        <v>0.1057935984325448</v>
       </c>
       <c r="R25">
-        <v>0.1098643988277756</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>42</v>
+        <v>0.1098643768926255</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>0.1154603476689546</v>
+        <v>0.1154603527987392</v>
       </c>
       <c r="C26">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D26">
-        <v>0.1156677329653147</v>
+        <v>0.115667739943293</v>
       </c>
       <c r="E26">
-        <v>0.1189848434177421</v>
+        <v>0.1189848465340648</v>
       </c>
       <c r="F26">
-        <v>0.1196998444109386</v>
+        <v>0.1196998506867343</v>
       </c>
       <c r="G26">
-        <v>0.11658692997545129</v>
+        <v>0.1165869363476578</v>
       </c>
       <c r="H26">
-        <v>0.1186296190077443</v>
+        <v>0.1186296238324843</v>
       </c>
       <c r="I26">
-        <v>0.1168627267040997</v>
+        <v>0.1168627297081488</v>
       </c>
       <c r="J26">
-        <v>0.1103764079203048</v>
+        <v>0.1103764109987394</v>
       </c>
       <c r="K26">
-        <v>0.11458052235400031</v>
+        <v>0.114580526827264</v>
       </c>
       <c r="L26">
-        <v>0.106415159200897</v>
+        <v>0.106415155848357</v>
       </c>
       <c r="M26">
-        <v>0.101082483625391</v>
+        <v>0.1010824708636255</v>
       </c>
       <c r="N26">
-        <v>0.1002243229315154</v>
+        <v>0.1002243213259729</v>
       </c>
       <c r="O26">
-        <v>0.1016414216462492</v>
+        <v>0.1016414118544414</v>
       </c>
       <c r="P26">
-        <v>0.10360679836216249</v>
+        <v>0.1036067836501457</v>
       </c>
       <c r="Q26">
-        <v>0.10717990374075501</v>
+        <v>0.1071798835378968</v>
       </c>
       <c r="R26">
-        <v>0.1121442343515473</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>43</v>
+        <v>0.1121442092881485</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>0.10307949997458581</v>
+        <v>0.1030795022160009</v>
       </c>
       <c r="C27">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D27">
-        <v>0.11576278608811461</v>
+        <v>0.115762791922182</v>
       </c>
       <c r="E27">
-        <v>0.1190606187183583</v>
+        <v>0.1190606207058079</v>
       </c>
       <c r="F27">
-        <v>0.1197440910153612</v>
+        <v>0.1197440954441691</v>
       </c>
       <c r="G27">
-        <v>0.11628815047951439</v>
+        <v>0.1162881574827185</v>
       </c>
       <c r="H27">
-        <v>0.1183924904087808</v>
+        <v>0.1183924956592919</v>
       </c>
       <c r="I27">
-        <v>0.11693460594792909</v>
+        <v>0.1169346093841649</v>
       </c>
       <c r="J27">
-        <v>0.1116254849675845</v>
+        <v>0.1116254895817792</v>
       </c>
       <c r="K27">
-        <v>0.1146294086685858</v>
+        <v>0.1146294137609978</v>
       </c>
       <c r="L27">
-        <v>0.1076377398265263</v>
+        <v>0.1076377352826778</v>
       </c>
       <c r="M27">
-        <v>9.951666724633465E-2</v>
+        <v>0.09951666961678836</v>
       </c>
       <c r="N27">
-        <v>9.6311936418000454E-2</v>
+        <v>0.09631193798586957</v>
       </c>
       <c r="O27">
-        <v>9.4161153367425976E-2</v>
+        <v>0.09416115103919935</v>
       </c>
       <c r="P27">
-        <v>9.2920641344178018E-2</v>
+        <v>0.09292063763720688</v>
       </c>
       <c r="Q27">
-        <v>9.4707036710045073E-2</v>
+        <v>0.09470703164174572</v>
       </c>
       <c r="R27">
-        <v>9.5152383755237116E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>44</v>
+        <v>0.09515237373918799</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>0.1078639793413442</v>
+        <v>0.1078639816439045</v>
       </c>
       <c r="C28">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D28">
-        <v>0.1155228501683777</v>
+        <v>0.1155228561655479</v>
       </c>
       <c r="E28">
-        <v>0.1183950445613753</v>
+        <v>0.118395049082166</v>
       </c>
       <c r="F28">
-        <v>0.1210570713249419</v>
+        <v>0.1210570785924569</v>
       </c>
       <c r="G28">
-        <v>0.1188467090685207</v>
+        <v>0.1188467157719291</v>
       </c>
       <c r="H28">
-        <v>0.1178498749131232</v>
+        <v>0.1178499324994225</v>
       </c>
       <c r="I28">
-        <v>0.1168791034352642</v>
+        <v>0.1168791130001791</v>
       </c>
       <c r="J28">
-        <v>0.1202923376175023</v>
+        <v>0.1202923437105168</v>
       </c>
       <c r="K28">
-        <v>0.119034159934109</v>
+        <v>0.1190341650067698</v>
       </c>
       <c r="L28">
-        <v>0.1156517083309323</v>
+        <v>0.1156517133804058</v>
       </c>
       <c r="M28">
-        <v>0.1027260768629837</v>
+        <v>0.1027260794413588</v>
       </c>
       <c r="N28">
-        <v>9.9921335803130062E-2</v>
+        <v>0.09992133781628676</v>
       </c>
       <c r="O28">
-        <v>9.8039729322197885E-2</v>
+        <v>0.09803973115975195</v>
       </c>
       <c r="P28">
-        <v>9.7407405016103468E-2</v>
+        <v>0.09740740364106229</v>
       </c>
       <c r="Q28">
-        <v>9.7168897117856576E-2</v>
+        <v>0.09716889509397496</v>
       </c>
       <c r="R28">
-        <v>9.7713847245056162E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>45</v>
+        <v>0.09771384385500539</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>0.10534320203489719</v>
+        <v>0.1053432043303216</v>
       </c>
       <c r="C29">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D29">
-        <v>0.1157097380288922</v>
+        <v>0.1157097438560448</v>
       </c>
       <c r="E29">
-        <v>0.1187669375724224</v>
+        <v>0.1187669402977369</v>
       </c>
       <c r="F29">
-        <v>0.12171800351177239</v>
+        <v>0.1217180111107215</v>
       </c>
       <c r="G29">
-        <v>0.11949043966270929</v>
+        <v>0.119490447742162</v>
       </c>
       <c r="H29">
-        <v>0.1182648287083061</v>
+        <v>0.1182648339638905</v>
       </c>
       <c r="I29">
-        <v>0.11711446778000451</v>
+        <v>0.117114473652733</v>
       </c>
       <c r="J29">
-        <v>0.1205572349283193</v>
+        <v>0.1205572407065866</v>
       </c>
       <c r="K29">
-        <v>0.1191595220559326</v>
+        <v>0.1191595271472178</v>
       </c>
       <c r="L29">
-        <v>0.1157786745576536</v>
+        <v>0.1157786830743652</v>
       </c>
       <c r="M29">
-        <v>0.1036379003967851</v>
+        <v>0.1036379028769759</v>
       </c>
       <c r="N29">
-        <v>0.10038566676255239</v>
+        <v>0.1003856676787941</v>
       </c>
       <c r="O29">
-        <v>9.7735853860065072E-2</v>
+        <v>0.09773585548737894</v>
       </c>
       <c r="P29">
-        <v>9.6827578642122103E-2</v>
+        <v>0.09682758066730532</v>
       </c>
       <c r="Q29">
-        <v>9.6201097689487161E-2</v>
+        <v>0.09620109561925551</v>
       </c>
       <c r="R29">
-        <v>9.5430200233689644E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>46</v>
+        <v>0.09543019667654652</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>0.10643979546896</v>
+        <v>0.1064397970928905</v>
       </c>
       <c r="C30">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D30">
-        <v>0.115854151599335</v>
+        <v>0.1158541575120282</v>
       </c>
       <c r="E30">
-        <v>0.11884772560428181</v>
+        <v>0.118847729400249</v>
       </c>
       <c r="F30">
-        <v>0.1213164406780203</v>
+        <v>0.1213164477109551</v>
       </c>
       <c r="G30">
-        <v>0.1191496283553603</v>
+        <v>0.1191496345803742</v>
       </c>
       <c r="H30">
-        <v>0.1180058818756488</v>
+        <v>0.1180058865805413</v>
       </c>
       <c r="I30">
-        <v>0.11700812192610489</v>
+        <v>0.1170081322636849</v>
       </c>
       <c r="J30">
-        <v>0.1201859293985373</v>
+        <v>0.1201859342259497</v>
       </c>
       <c r="K30">
-        <v>0.1184563471984328</v>
+        <v>0.1184563551466698</v>
       </c>
       <c r="L30">
-        <v>0.115766004903884</v>
+        <v>0.1157660123757443</v>
       </c>
       <c r="M30">
-        <v>0.10370705975805281</v>
+        <v>0.1037070617079751</v>
       </c>
       <c r="N30">
-        <v>0.1003093863643391</v>
+        <v>0.1003093877856941</v>
       </c>
       <c r="O30">
-        <v>9.7925026897963466E-2</v>
+        <v>0.0979250285219119</v>
       </c>
       <c r="P30">
-        <v>9.6600059124120743E-2</v>
+        <v>0.09660005817839003</v>
       </c>
       <c r="Q30">
-        <v>9.5447170126730846E-2</v>
+        <v>0.09544716949268831</v>
       </c>
       <c r="R30">
-        <v>9.4728661827965646E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>47</v>
+        <v>0.09472865848020132</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>0.1065521433445837</v>
+        <v>0.1065521446469596</v>
       </c>
       <c r="C31">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D31">
-        <v>0.1154380817369471</v>
+        <v>0.1154380881617699</v>
       </c>
       <c r="E31">
-        <v>0.11809624199990559</v>
+        <v>0.1180962422930877</v>
       </c>
       <c r="F31">
-        <v>0.120975247813305</v>
+        <v>0.120975254206546</v>
       </c>
       <c r="G31">
-        <v>0.1186880784707306</v>
+        <v>0.118688085363171</v>
       </c>
       <c r="H31">
-        <v>0.11772115048526779</v>
+        <v>0.1177211553561485</v>
       </c>
       <c r="I31">
-        <v>0.1167327172479098</v>
+        <v>0.1167327221994134</v>
       </c>
       <c r="J31">
-        <v>0.1201572646475212</v>
+        <v>0.1201572701772938</v>
       </c>
       <c r="K31">
-        <v>0.1195537283258389</v>
+        <v>0.1195537339867662</v>
       </c>
       <c r="L31">
-        <v>0.11682881477700729</v>
+        <v>0.1168288148657047</v>
       </c>
       <c r="M31">
-        <v>0.1052552764300858</v>
+        <v>0.1052552789905793</v>
       </c>
       <c r="N31">
-        <v>0.10182069911995641</v>
+        <v>0.1018206991063277</v>
       </c>
       <c r="O31">
-        <v>9.9842561744339142E-2</v>
+        <v>0.09984256286989489</v>
       </c>
       <c r="P31">
-        <v>9.7622705666795609E-2</v>
+        <v>0.09762270780853459</v>
       </c>
       <c r="Q31">
-        <v>9.6753834866186494E-2</v>
+        <v>0.0967538363464599</v>
       </c>
       <c r="R31">
-        <v>9.5391427478880894E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>48</v>
+        <v>0.09539142684190816</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>0.10708659106605289</v>
+        <v>0.1070865931302612</v>
       </c>
       <c r="C32">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D32">
-        <v>0.1155044702074092</v>
+        <v>0.1155044763476981</v>
       </c>
       <c r="E32">
-        <v>0.11855056606642771</v>
+        <v>0.1185505703011505</v>
       </c>
       <c r="F32">
-        <v>0.1214646439352414</v>
+        <v>0.1214646507435238</v>
       </c>
       <c r="G32">
-        <v>0.1191628102905553</v>
+        <v>0.1191628121014948</v>
       </c>
       <c r="H32">
-        <v>0.1178561587547144</v>
+        <v>0.1178561622449318</v>
       </c>
       <c r="I32">
-        <v>0.11657857387928081</v>
+        <v>0.1165785756585527</v>
       </c>
       <c r="J32">
-        <v>0.1199109786876509</v>
+        <v>0.1199109841068158</v>
       </c>
       <c r="K32">
-        <v>0.1181635158547636</v>
+        <v>0.1181635205722941</v>
       </c>
       <c r="L32">
-        <v>0.11473709010956221</v>
+        <v>0.1147370949806299</v>
       </c>
       <c r="M32">
-        <v>0.1018203263534921</v>
+        <v>0.1018203274137398</v>
       </c>
       <c r="N32">
-        <v>9.9270812888538992E-2</v>
+        <v>0.09927081364591116</v>
       </c>
       <c r="O32">
-        <v>9.7714437300776905E-2</v>
+        <v>0.09771443658420118</v>
       </c>
       <c r="P32">
-        <v>9.7683444181191126E-2</v>
+        <v>0.09768344328232921</v>
       </c>
       <c r="Q32">
-        <v>9.8520782719623043E-2</v>
+        <v>0.09852077995158266</v>
       </c>
       <c r="R32">
-        <v>9.933266557815365E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>49</v>
+        <v>0.09933265898472386</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>0.1083586230560649</v>
+        <v>0.1083586246546232</v>
       </c>
       <c r="C33">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D33">
-        <v>0.11582756907989809</v>
+        <v>0.1158275748042084</v>
       </c>
       <c r="E33">
-        <v>0.11895491781416739</v>
+        <v>0.1189549210081539</v>
       </c>
       <c r="F33">
-        <v>0.12176461593983</v>
+        <v>0.1217646119231251</v>
       </c>
       <c r="G33">
-        <v>0.1195796134369848</v>
+        <v>0.119579619475957</v>
       </c>
       <c r="H33">
-        <v>0.1182098323910471</v>
+        <v>0.1182098372239659</v>
       </c>
       <c r="I33">
-        <v>0.117351875741443</v>
+        <v>0.117351881516032</v>
       </c>
       <c r="J33">
-        <v>0.1207189354103374</v>
+        <v>0.1207189400122831</v>
       </c>
       <c r="K33">
-        <v>0.1190493209084048</v>
+        <v>0.1190493267576176</v>
       </c>
       <c r="L33">
-        <v>0.1157922069122425</v>
+        <v>0.1157922118161503</v>
       </c>
       <c r="M33">
-        <v>0.1037735223336362</v>
+        <v>0.1037735238229916</v>
       </c>
       <c r="N33">
-        <v>0.1007127778117715</v>
+        <v>0.1007127783194432</v>
       </c>
       <c r="O33">
-        <v>9.8917841683235766E-2</v>
+        <v>0.09891784040436322</v>
       </c>
       <c r="P33">
-        <v>9.8373360568640295E-2</v>
+        <v>0.09837335915879801</v>
       </c>
       <c r="Q33">
-        <v>9.8845269949422943E-2</v>
+        <v>0.09884526548069203</v>
       </c>
       <c r="R33">
-        <v>9.9581094859724675E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>50</v>
+        <v>0.09958108894513656</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>0.1090088169362744</v>
+        <v>0.1090088187865129</v>
       </c>
       <c r="C34">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D34">
-        <v>0.1157282156173385</v>
+        <v>0.115728222545899</v>
       </c>
       <c r="E34">
-        <v>0.1189607131436744</v>
+        <v>0.1189607145175135</v>
       </c>
       <c r="F34">
-        <v>0.12183203572925</v>
+        <v>0.1218320427930535</v>
       </c>
       <c r="G34">
-        <v>0.119362284876405</v>
+        <v>0.1193622905442678</v>
       </c>
       <c r="H34">
-        <v>0.1183301489578398</v>
+        <v>0.1183301523578435</v>
       </c>
       <c r="I34">
-        <v>0.1172633682760767</v>
+        <v>0.1172633740638196</v>
       </c>
       <c r="J34">
-        <v>0.12093972119630381</v>
+        <v>0.1209397270934923</v>
       </c>
       <c r="K34">
-        <v>0.1188949329156261</v>
+        <v>0.1188949392484151</v>
       </c>
       <c r="L34">
-        <v>0.1157636830522045</v>
+        <v>0.1157636888942405</v>
       </c>
       <c r="M34">
-        <v>0.1048473515685075</v>
+        <v>0.1048473542297882</v>
       </c>
       <c r="N34">
-        <v>0.1013942663053736</v>
+        <v>0.1013942682332793</v>
       </c>
       <c r="O34">
-        <v>9.9500065018896341E-2</v>
+        <v>0.09950006498339868</v>
       </c>
       <c r="P34">
-        <v>9.826225713088671E-2</v>
+        <v>0.09826226126636951</v>
       </c>
       <c r="Q34">
-        <v>9.8232152135205586E-2</v>
+        <v>0.09823215012872426</v>
       </c>
       <c r="R34">
-        <v>9.8833832637502242E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>51</v>
+        <v>0.09883382907055918</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>0.1090626460652008</v>
+        <v>0.1090626489527469</v>
       </c>
       <c r="C35">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D35">
-        <v>0.1157259154416011</v>
+        <v>0.1157259220271784</v>
       </c>
       <c r="E35">
-        <v>0.118472736126836</v>
+        <v>0.1184727392260431</v>
       </c>
       <c r="F35">
-        <v>0.1212438167311455</v>
+        <v>0.1212438240477035</v>
       </c>
       <c r="G35">
-        <v>0.1190515904432215</v>
+        <v>0.1190515938877672</v>
       </c>
       <c r="H35">
-        <v>0.11794013756654979</v>
+        <v>0.1179401348165522</v>
       </c>
       <c r="I35">
-        <v>0.11699103839193049</v>
+        <v>0.1169910441196064</v>
       </c>
       <c r="J35">
-        <v>0.1208145464760409</v>
+        <v>0.1208145513824216</v>
       </c>
       <c r="K35">
-        <v>0.1194759332495901</v>
+        <v>0.119475940772497</v>
       </c>
       <c r="L35">
-        <v>0.11623599289686121</v>
+        <v>0.1162359983890768</v>
       </c>
       <c r="M35">
-        <v>0.10392513352168679</v>
+        <v>0.1039251364923445</v>
       </c>
       <c r="N35">
-        <v>0.10119864185797919</v>
+        <v>0.101198643786964</v>
       </c>
       <c r="O35">
-        <v>9.9000173073253137E-2</v>
+        <v>0.0990001743205977</v>
       </c>
       <c r="P35">
-        <v>9.8238568114030547E-2</v>
+        <v>0.09823856915502138</v>
       </c>
       <c r="Q35">
-        <v>9.8310750298431115E-2</v>
+        <v>0.0983107486854753</v>
       </c>
       <c r="R35">
-        <v>9.8240792537470423E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>52</v>
+        <v>0.09824078840668241</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>0.10793810865099571</v>
+        <v>0.1079381105164877</v>
       </c>
       <c r="C36">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D36">
-        <v>0.1157571304705831</v>
+        <v>0.1157571364552739</v>
       </c>
       <c r="E36">
-        <v>0.1188483935450978</v>
+        <v>0.1188483978539543</v>
       </c>
       <c r="F36">
-        <v>0.1213403752090928</v>
+        <v>0.1213403813790831</v>
       </c>
       <c r="G36">
-        <v>0.1192013755659535</v>
+        <v>0.1192013793142759</v>
       </c>
       <c r="H36">
-        <v>0.1181139580923856</v>
+        <v>0.1181139544989024</v>
       </c>
       <c r="I36">
-        <v>0.11713976698656189</v>
+        <v>0.1171397644481062</v>
       </c>
       <c r="J36">
-        <v>0.12031547478198169</v>
+        <v>0.1203154813172372</v>
       </c>
       <c r="K36">
-        <v>0.1188771078293387</v>
+        <v>0.1188771135769994</v>
       </c>
       <c r="L36">
-        <v>0.1162311044328552</v>
+        <v>0.1162311093680188</v>
       </c>
       <c r="M36">
-        <v>0.10593249017669119</v>
+        <v>0.105932492531544</v>
       </c>
       <c r="N36">
-        <v>0.1013882469126695</v>
+        <v>0.1013882486007893</v>
       </c>
       <c r="O36">
-        <v>9.9854867383549234E-2</v>
+        <v>0.09985486843614139</v>
       </c>
       <c r="P36">
-        <v>9.7495703948726142E-2</v>
+        <v>0.0974957058880514</v>
       </c>
       <c r="Q36">
-        <v>9.6716073862838273E-2</v>
+        <v>0.09671607450871163</v>
       </c>
       <c r="R36">
-        <v>9.4850231362297366E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>53</v>
+        <v>0.09485023017889305</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>0.1195484345397769</v>
+        <v>0.1195484388634738</v>
       </c>
       <c r="C37">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D37">
-        <v>0.1183327416305613</v>
+        <v>0.1183327462637301</v>
       </c>
       <c r="E37">
-        <v>0.12231128641207389</v>
+        <v>0.1223112935311386</v>
       </c>
       <c r="F37">
-        <v>0.11844752113463509</v>
+        <v>0.1184475275109951</v>
       </c>
       <c r="G37">
-        <v>0.11368367978258451</v>
+        <v>0.1136836874402101</v>
       </c>
       <c r="H37">
-        <v>0.1173173298063505</v>
+        <v>0.1173173349079883</v>
       </c>
       <c r="I37">
-        <v>0.11425719055873459</v>
+        <v>0.1142571928357993</v>
       </c>
       <c r="J37">
-        <v>0.1091921020926483</v>
+        <v>0.1091920958556408</v>
       </c>
       <c r="K37">
-        <v>0.10708346356282181</v>
+        <v>0.1070834548942175</v>
       </c>
       <c r="L37">
-        <v>0.1074079522815387</v>
+        <v>0.1074079424228211</v>
       </c>
       <c r="M37">
-        <v>0.1070329549323816</v>
+        <v>0.1070329402898406</v>
       </c>
       <c r="N37">
-        <v>0.10762761625834839</v>
+        <v>0.1076276023577355</v>
       </c>
       <c r="O37">
-        <v>0.1100654273916586</v>
+        <v>0.1100654072384148</v>
       </c>
       <c r="P37">
-        <v>0.10874781557496151</v>
+        <v>0.1087477835588333</v>
       </c>
       <c r="Q37">
-        <v>0.1087051639697353</v>
+        <v>0.1087051176054776</v>
       </c>
       <c r="R37">
-        <v>0.10865203530403809</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>54</v>
+        <v>0.1086519805225209</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>0.1035783457621379</v>
+        <v>0.1035783521585383</v>
       </c>
       <c r="C38">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D38">
-        <v>0.11688858906156829</v>
+        <v>0.1168885934240411</v>
       </c>
       <c r="E38">
-        <v>0.1212365018643663</v>
+        <v>0.1212365087501983</v>
       </c>
       <c r="F38">
-        <v>0.1196734325606402</v>
+        <v>0.1196734477030059</v>
       </c>
       <c r="G38">
-        <v>0.1116037225209847</v>
+        <v>0.1116037225163964</v>
       </c>
       <c r="H38">
-        <v>0.1102012842979256</v>
+        <v>0.1102012888244302</v>
       </c>
       <c r="I38">
-        <v>0.1029804868616797</v>
+        <v>0.1029804918121413</v>
       </c>
       <c r="J38">
-        <v>9.5246756419065229E-2</v>
+        <v>0.09524675867793243</v>
       </c>
       <c r="K38">
-        <v>9.5350082095608815E-2</v>
+        <v>0.09535008059086028</v>
       </c>
       <c r="L38">
-        <v>9.7802565193118834E-2</v>
+        <v>0.09780256374605871</v>
       </c>
       <c r="M38">
-        <v>0.10021220605491291</v>
+        <v>0.1002121998447567</v>
       </c>
       <c r="N38">
-        <v>0.1005706711082644</v>
+        <v>0.1005706617095752</v>
       </c>
       <c r="O38">
-        <v>0.10122555770121031</v>
+        <v>0.1012255470514919</v>
       </c>
       <c r="P38">
-        <v>0.1010685294520564</v>
+        <v>0.1010685172977868</v>
       </c>
       <c r="Q38">
-        <v>0.1001505330342036</v>
+        <v>0.1001505246797339</v>
       </c>
       <c r="R38">
-        <v>9.9629838538216484E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>55</v>
+        <v>0.09962982734250309</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>0.1060328019866742</v>
+        <v>0.1060328058127269</v>
       </c>
       <c r="C39">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D39">
-        <v>0.1166170249972721</v>
+        <v>0.1166170297173704</v>
       </c>
       <c r="E39">
-        <v>0.1204974777614666</v>
+        <v>0.120497483485739</v>
       </c>
       <c r="F39">
-        <v>0.1184093007578297</v>
+        <v>0.1184093053781546</v>
       </c>
       <c r="G39">
-        <v>0.11146149454794781</v>
+        <v>0.1114614944547568</v>
       </c>
       <c r="H39">
-        <v>0.1112993390828092</v>
+        <v>0.1112993446770388</v>
       </c>
       <c r="I39">
-        <v>0.104960074241915</v>
+        <v>0.1049600801121239</v>
       </c>
       <c r="J39">
-        <v>9.724389388364911E-2</v>
+        <v>0.09724389768908612</v>
       </c>
       <c r="K39">
-        <v>9.7770681422474165E-2</v>
+        <v>0.09777068305873166</v>
       </c>
       <c r="L39">
-        <v>9.7210024481273721E-2</v>
+        <v>0.09721002388985434</v>
       </c>
       <c r="M39">
-        <v>9.7671456952657804E-2</v>
+        <v>0.09767145335618287</v>
       </c>
       <c r="N39">
-        <v>9.8849471908683928E-2</v>
+        <v>0.0988494667705061</v>
       </c>
       <c r="O39">
-        <v>9.749637843697577E-2</v>
+        <v>0.09749636061693372</v>
       </c>
       <c r="P39">
-        <v>9.8529003075246813E-2</v>
+        <v>0.09852893521497905</v>
       </c>
       <c r="Q39">
-        <v>9.9335753873602786E-2</v>
+        <v>0.09933574176828029</v>
       </c>
       <c r="R39">
-        <v>9.8969866848868618E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>56</v>
+        <v>0.09896985080237085</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>0.1172110678075253</v>
+        <v>0.1172110736281749</v>
       </c>
       <c r="C40">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D40">
-        <v>0.1177261778601524</v>
+        <v>0.1177261824477248</v>
       </c>
       <c r="E40">
-        <v>0.11618647417079229</v>
+        <v>0.1161864778912317</v>
       </c>
       <c r="F40">
-        <v>0.1119643250494341</v>
+        <v>0.111964331654437</v>
       </c>
       <c r="G40">
-        <v>0.11332894024667919</v>
+        <v>0.1133289419776706</v>
       </c>
       <c r="H40">
-        <v>0.1064125971596927</v>
+        <v>0.106412602760743</v>
       </c>
       <c r="I40">
-        <v>0.1027654642063377</v>
+        <v>0.1027654658893347</v>
       </c>
       <c r="J40">
-        <v>0.1027551580605041</v>
+        <v>0.1027551550156183</v>
       </c>
       <c r="K40">
-        <v>0.10512171760652519</v>
+        <v>0.1051217088877572</v>
       </c>
       <c r="L40">
-        <v>0.1049896556358484</v>
+        <v>0.1049896450562288</v>
       </c>
       <c r="M40">
-        <v>0.1028086590309651</v>
+        <v>0.1028086461826608</v>
       </c>
       <c r="N40">
-        <v>0.10325615101311519</v>
+        <v>0.1032561381079942</v>
       </c>
       <c r="O40">
-        <v>0.1021352542058514</v>
+        <v>0.1021352378109852</v>
       </c>
       <c r="P40">
-        <v>0.1031501199929739</v>
+        <v>0.1031500943395658</v>
       </c>
       <c r="Q40">
-        <v>0.1049280512462112</v>
+        <v>0.1049280196525696</v>
       </c>
       <c r="R40">
-        <v>0.1086699031616726</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>57</v>
+        <v>0.1086698602547106</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>0.1183939615298254</v>
+        <v>0.1183939695957617</v>
       </c>
       <c r="C41">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D41">
-        <v>0.11826959533494349</v>
+        <v>0.118269603516369</v>
       </c>
       <c r="E41">
-        <v>0.12592848529298861</v>
+        <v>0.1259284903418242</v>
       </c>
       <c r="F41">
-        <v>0.12122807271517309</v>
+        <v>0.1212280794712725</v>
       </c>
       <c r="G41">
-        <v>0.12108194687038749</v>
+        <v>0.1210819533423566</v>
       </c>
       <c r="H41">
-        <v>0.11676840830926941</v>
+        <v>0.1167684141825981</v>
       </c>
       <c r="I41">
-        <v>0.1158562369296436</v>
+        <v>0.1158562442145225</v>
       </c>
       <c r="J41">
-        <v>0.1142933392317569</v>
+        <v>0.1142933429062367</v>
       </c>
       <c r="K41">
-        <v>0.1116813423787326</v>
+        <v>0.1116813452034928</v>
       </c>
       <c r="L41">
-        <v>0.11378444885544479</v>
+        <v>0.1137844502619664</v>
       </c>
       <c r="M41">
-        <v>0.1153964917224045</v>
+        <v>0.1153964924543943</v>
       </c>
       <c r="N41">
-        <v>0.1154791235609606</v>
+        <v>0.1154791212607945</v>
       </c>
       <c r="O41">
-        <v>0.11661595021680191</v>
+        <v>0.116615944589384</v>
       </c>
       <c r="P41">
-        <v>0.1193855289177622</v>
+        <v>0.1193855219615932</v>
       </c>
       <c r="Q41">
-        <v>0.11973510360733471</v>
+        <v>0.1197350952951201</v>
       </c>
       <c r="R41">
-        <v>0.1204554720906916</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>58</v>
+        <v>0.1204554621206269</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>0.1068112328529485</v>
+        <v>0.1068112364301166</v>
       </c>
       <c r="C42">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D42">
-        <v>0.1132781852425202</v>
+        <v>0.1132781914885924</v>
       </c>
       <c r="E42">
-        <v>0.1285213936045628</v>
+        <v>0.1285214043264616</v>
       </c>
       <c r="F42">
-        <v>0.12237326208505921</v>
+        <v>0.1223732697196777</v>
       </c>
       <c r="G42">
-        <v>0.1092213511077231</v>
+        <v>0.1092213583794298</v>
       </c>
       <c r="H42">
-        <v>0.10479109859705329</v>
+        <v>0.1047911058894344</v>
       </c>
       <c r="I42">
-        <v>0.1017724392643653</v>
+        <v>0.101772442524049</v>
       </c>
       <c r="J42">
-        <v>9.6395489824880456E-2</v>
+        <v>0.09639549381358366</v>
       </c>
       <c r="K42">
-        <v>9.5664090345589009E-2</v>
+        <v>0.09566409310945605</v>
       </c>
       <c r="L42">
-        <v>9.7094222743773315E-2</v>
+        <v>0.09709422341243462</v>
       </c>
       <c r="M42">
-        <v>9.5643015561415287E-2</v>
+        <v>0.09564301668519083</v>
       </c>
       <c r="N42">
-        <v>9.5826955399479483E-2</v>
+        <v>0.09582695896809602</v>
       </c>
       <c r="O42">
-        <v>9.6937016280570082E-2</v>
+        <v>0.09693701071145283</v>
       </c>
       <c r="P42">
-        <v>9.7424602079681039E-2</v>
+        <v>0.09742459405206011</v>
       </c>
       <c r="Q42">
-        <v>9.7089746805650148E-2</v>
+        <v>0.09708973635890791</v>
       </c>
       <c r="R42">
-        <v>9.8186756622749977E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>59</v>
+        <v>0.09818674446530494</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>0.1060287226691259</v>
+        <v>0.1060287293814527</v>
       </c>
       <c r="C43">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D43">
-        <v>0.1157773059681165</v>
+        <v>0.1157773144850335</v>
       </c>
       <c r="E43">
-        <v>0.11815387164177669</v>
+        <v>0.1181538780682643</v>
       </c>
       <c r="F43">
-        <v>0.11247605171897131</v>
+        <v>0.1124760543229183</v>
       </c>
       <c r="G43">
-        <v>0.11037131284996129</v>
+        <v>0.1103713190097477</v>
       </c>
       <c r="H43">
-        <v>0.101422318512275</v>
+        <v>0.1014223252672364</v>
       </c>
       <c r="I43">
-        <v>9.8085250132904436E-2</v>
+        <v>0.09808525565987583</v>
       </c>
       <c r="J43">
-        <v>9.6104555756950899E-2</v>
+        <v>0.09610456082984686</v>
       </c>
       <c r="K43">
-        <v>9.6605100761408699E-2</v>
+        <v>0.09660510624705938</v>
       </c>
       <c r="L43">
-        <v>9.8789957503462117E-2</v>
+        <v>0.09878995947099846</v>
       </c>
       <c r="M43">
-        <v>9.6139848239840259E-2</v>
+        <v>0.09613985046860364</v>
       </c>
       <c r="N43">
-        <v>9.5937564339746234E-2</v>
+        <v>0.09593756431822155</v>
       </c>
       <c r="O43">
-        <v>9.5831238215935602E-2</v>
+        <v>0.09583123618301853</v>
       </c>
       <c r="P43">
-        <v>9.6810884172035802E-2</v>
+        <v>0.09681088067058038</v>
       </c>
       <c r="Q43">
-        <v>9.8042413219205996E-2</v>
+        <v>0.09804240798815002</v>
       </c>
       <c r="R43">
-        <v>9.9160467291833074E-2</v>
+        <v>0.09916046646531454</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:R43">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>